--- a/ig/DM-JUIN-2025/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
+++ b/ig/DM-JUIN-2025/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
@@ -344,7 +344,7 @@
     <t>FON-60</t>
   </si>
   <si>
-    <t>Pharmacien remplaçant Bonnes Pratiques de Dispensation d'Oxygène</t>
+    <t>Pharmacien remplaçant BPDO</t>
   </si>
   <si>
     <t>FON-AU</t>
